--- a/Other Reports/BCIS309 Project Timeframe.xlsx
+++ b/Other Reports/BCIS309 Project Timeframe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tewaka-my.sharepoint.com/personal/dmm0416_arastudent_ac_nz/Documents/2026 S1/BCIS309 Capstone/Weekly Reports/Weekly Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tewaka-my.sharepoint.com/personal/dmm0416_arastudent_ac_nz/Documents/2026 S1/BCIS309 Capstone/Git/BCIS309/Other Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="401" documentId="8_{F67DA2EB-83DD-42AC-9A1D-5037C265386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F6E9DE-4ACB-4BC7-87DE-31E4E0530616}"/>
+  <xr:revisionPtr revIDLastSave="407" documentId="8_{F67DA2EB-83DD-42AC-9A1D-5037C265386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B72B6303-63B8-421A-8738-C90434391185}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{EA32EB52-33D6-4050-96A2-43A6F8B7B4B8}"/>
+    <workbookView minimized="1" xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="9420" activeTab="1" xr2:uid="{EA32EB52-33D6-4050-96A2-43A6F8B7B4B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Calendar" sheetId="2" r:id="rId1"/>
@@ -1706,10 +1706,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Hours &amp; Burndown'!$H$4:$H$15</c:f>
+              <c:f>'Hours &amp; Burndown'!$H$4:$H$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>150</c:v>
                 </c:pt>
@@ -1745,6 +1745,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2472,10 +2475,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Hours &amp; Burndown'!$M$4:$M$15</c:f>
+              <c:f>'Hours &amp; Burndown'!$M$4:$M$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>300</c:v>
                 </c:pt>
@@ -2511,6 +2514,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>166</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5856,16 +5862,22 @@
       <c r="E16">
         <v>6</v>
       </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
       <c r="G16">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="H16">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J16">
         <v>24</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
       </c>
       <c r="L16">
         <f t="shared" si="2"/>
@@ -5873,7 +5885,7 @@
       </c>
       <c r="M16">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -5893,7 +5905,7 @@
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J17">
         <v>24</v>
@@ -5904,7 +5916,7 @@
       </c>
       <c r="M17">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -5924,7 +5936,7 @@
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J18">
         <v>24</v>
@@ -5935,7 +5947,7 @@
       </c>
       <c r="M18">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -5955,7 +5967,7 @@
       </c>
       <c r="H19">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J19">
         <v>24</v>
@@ -5966,7 +5978,7 @@
       </c>
       <c r="M19">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -5986,7 +5998,7 @@
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J20">
         <v>24</v>
@@ -5997,7 +6009,7 @@
       </c>
       <c r="M20">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -6017,7 +6029,7 @@
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J21">
         <v>24</v>
@@ -6028,7 +6040,7 @@
       </c>
       <c r="M21">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -6048,7 +6060,7 @@
       </c>
       <c r="H22">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="M22">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -6081,7 +6093,7 @@
       </c>
       <c r="H23">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -6092,7 +6104,7 @@
       </c>
       <c r="M23">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -6114,7 +6126,7 @@
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -6125,24 +6137,24 @@
       </c>
       <c r="M24">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="F25">
-        <f>SUM(F5:F15)</f>
-        <v>79</v>
+        <f>SUM(F5:F16)</f>
+        <v>95</v>
       </c>
       <c r="K25">
         <f>SUM(K5:K24)</f>
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s">
         <v>64</v>
       </c>
       <c r="M25">
         <f>SUM(F25,K25)</f>
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
